--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:34:08+00:00</t>
+    <t>2026-04-15T07:49:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T07:49:49+00:00</t>
+    <t>2026-04-16T07:52:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:52:47+00:00</t>
+    <t>2026-04-16T09:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:27:41+00:00</t>
+    <t>2026-04-16T09:55:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T09:55:40+00:00</t>
+    <t>2026-04-16T10:39:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T10:39:58+00:00</t>
+    <t>2026-04-17T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T08:40:59+00:00</t>
+    <t>2026-04-17T11:35:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
+++ b/fusionSectionsCDA/ig/StructureDefinition-fr-cda-evaluation-composant.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$172</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5040" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5389" uniqueCount="473">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T11:35:08+00:00</t>
+    <t>2026-04-20T14:26:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -556,6 +556,132 @@
     <t>http://terminology.hl7.org/ValueSet/v3-ObservationType</t>
   </si>
   <si>
+    <t>Observation.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Observation.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Observation.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
     <t>Observation.derivationExpr</t>
   </si>
   <si>
@@ -566,10 +692,6 @@
     <t>Observation.text</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
-</t>
-  </si>
-  <si>
     <t>Partie narrative</t>
   </si>
   <si>
@@ -719,123 +841,34 @@
     <t>Observation.statusCode.code</t>
   </si>
   <si>
-    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
-  </si>
-  <si>
     <t>completed</t>
   </si>
   <si>
-    <t>CD.code</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystem</t>
   </si>
   <si>
-    <t>Code System</t>
-  </si>
-  <si>
-    <t>Specifies the code system that defines the code.</t>
-  </si>
-  <si>
-    <t>CD.codeSystem</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystemName</t>
   </si>
   <si>
-    <t>Code System Name</t>
-  </si>
-  <si>
-    <t>The common name of the coding system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemName</t>
-  </si>
-  <si>
     <t>Observation.statusCode.codeSystemVersion</t>
   </si>
   <si>
-    <t>Code System Version</t>
-  </si>
-  <si>
-    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemVersion</t>
-  </si>
-  <si>
     <t>Observation.statusCode.displayName</t>
   </si>
   <si>
-    <t>Display Name</t>
-  </si>
-  <si>
-    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
-  </si>
-  <si>
-    <t>CD.displayName</t>
-  </si>
-  <si>
     <t>Observation.statusCode.sdtcValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
-</t>
-  </si>
-  <si>
-    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.valueSet</t>
-  </si>
-  <si>
     <t>Observation.statusCode.sdtcValueSetVersion</t>
   </si>
   <si>
-    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.sdtcValueSetVersion</t>
-  </si>
-  <si>
     <t>Observation.statusCode.originalText</t>
   </si>
   <si>
-    <t>Original Text</t>
-  </si>
-  <si>
-    <t>The text or phrase used as the basis for the coding.</t>
-  </si>
-  <si>
-    <t>CD.originalText</t>
-  </si>
-  <si>
     <t>Observation.statusCode.qualifier</t>
   </si>
   <si>
-    <t>Qualifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
-</t>
-  </si>
-  <si>
-    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
-  </si>
-  <si>
-    <t>CD.qualifier</t>
-  </si>
-  <si>
     <t>Observation.statusCode.translation</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
-  </si>
-  <si>
-    <t>CD.translation</t>
   </si>
   <si>
     <t>Observation.effectiveTime</t>
@@ -1764,7 +1797,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK161"/>
+  <dimension ref="A1:AK172"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="71.328125" customWidth="true" bestFit="true"/>
@@ -5083,7 +5116,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>167</v>
       </c>
@@ -5102,7 +5135,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -5397,7 +5430,9 @@
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E36" s="2"/>
+      <c r="E36" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
       </c>
@@ -5414,10 +5449,12 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>177</v>
+        <v>85</v>
       </c>
       <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
+      <c r="M36" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5443,13 +5480,11 @@
         <v>74</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>74</v>
@@ -5467,7 +5502,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5487,16 +5522,18 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E37" s="2"/>
+      <c r="E37" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F37" t="s" s="2">
         <v>75</v>
       </c>
@@ -5513,12 +5550,12 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="M37" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5568,7 +5605,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5586,28 +5623,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>84</v>
+        <v>181</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5616,11 +5653,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>86</v>
+        <v>182</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5647,11 +5684,13 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -5669,7 +5708,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>89</v>
+        <v>183</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5689,17 +5728,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5717,11 +5756,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5748,11 +5787,13 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -5770,7 +5811,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5790,17 +5831,17 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E40" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F40" t="s" s="2">
         <v>80</v>
@@ -5818,7 +5859,7 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
@@ -5891,7 +5932,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>192</v>
       </c>
@@ -5912,7 +5953,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5921,7 +5962,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
@@ -5952,29 +5993,31 @@
         <v>74</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5994,18 +6037,16 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" t="s" s="2">
-        <v>198</v>
-      </c>
+      <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
@@ -6022,11 +6063,11 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>85</v>
+        <v>197</v>
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6077,7 +6118,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6097,18 +6138,16 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" t="s" s="2">
-        <v>202</v>
-      </c>
+      <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
@@ -6125,11 +6164,11 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6156,11 +6195,13 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>204</v>
+        <v>74</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -6178,7 +6219,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6198,16 +6239,18 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" s="2"/>
+      <c r="E44" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
@@ -6224,10 +6267,12 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
+      <c r="M44" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6253,29 +6298,31 @@
         <v>74</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y44" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6295,21 +6342,23 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E45" s="2"/>
+      <c r="E45" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>74</v>
@@ -6321,17 +6370,13 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L45" t="s" s="2">
         <v>210</v>
       </c>
+      <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="N45" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>74</v>
@@ -6380,13 +6425,13 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>74</v>
@@ -6400,23 +6445,23 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F46" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>74</v>
@@ -6428,11 +6473,11 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6483,13 +6528,13 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>74</v>
@@ -6503,18 +6548,16 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E47" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>80</v>
       </c>
@@ -6531,12 +6574,10 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="L47" s="2"/>
-      <c r="M47" t="s" s="2">
-        <v>221</v>
-      </c>
+      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6586,7 +6627,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6606,10 +6647,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6632,14 +6673,12 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>91</v>
+        <v>205</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6665,11 +6704,13 @@
         <v>74</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>226</v>
+        <v>74</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>74</v>
@@ -6687,7 +6728,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6707,10 +6748,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6808,17 +6849,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>62</v>
+        <v>223</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>80</v>
@@ -6840,7 +6881,7 @@
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6852,7 +6893,7 @@
         <v>74</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>230</v>
+        <v>74</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>74</v>
@@ -6867,13 +6908,11 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>74</v>
+        <v>225</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -6891,7 +6930,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6911,23 +6950,23 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>74</v>
@@ -6939,11 +6978,11 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>112</v>
+        <v>229</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6994,7 +7033,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7014,23 +7053,23 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>74</v>
@@ -7042,11 +7081,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7073,13 +7112,11 @@
         <v>74</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>74</v>
+        <v>235</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>74</v>
@@ -7097,7 +7134,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7117,23 +7154,23 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>74</v>
@@ -7145,11 +7182,11 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7200,7 +7237,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -7220,23 +7257,23 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>74</v>
@@ -7248,11 +7285,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7279,13 +7316,11 @@
         <v>74</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>74</v>
+        <v>244</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>74</v>
@@ -7303,7 +7338,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -7323,10 +7358,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7349,12 +7384,10 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>249</v>
+        <v>85</v>
       </c>
       <c r="L55" s="2"/>
-      <c r="M55" t="s" s="2">
-        <v>250</v>
-      </c>
+      <c r="M55" s="2"/>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7380,13 +7413,11 @@
         <v>74</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>74</v>
@@ -7404,7 +7435,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -7424,10 +7455,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7452,11 +7483,15 @@
       <c r="K56" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L56" s="2"/>
+      <c r="L56" t="s" s="2">
+        <v>250</v>
+      </c>
       <c r="M56" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>74</v>
@@ -7505,7 +7540,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7525,35 +7560,35 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E57" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="F57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K57" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="F57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
@@ -7644,7 +7679,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>74</v>
@@ -7656,11 +7691,11 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>261</v>
+        <v>205</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7711,59 +7746,59 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>264</v>
-      </c>
       <c r="B59" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E59" t="s" s="2">
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M59" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="F59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L59" s="2"/>
-      <c r="M59" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7790,13 +7825,11 @@
         <v>74</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>74</v>
+        <v>266</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>74</v>
@@ -7814,44 +7847,46 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AG59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>268</v>
-      </c>
       <c r="B60" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E60" s="2"/>
+      <c r="E60" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F60" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>74</v>
@@ -7860,13 +7895,11 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>270</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>270</v>
+        <v>86</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7893,13 +7926,11 @@
         <v>74</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>74</v>
@@ -7917,7 +7948,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>268</v>
+        <v>89</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7937,16 +7968,18 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E61" s="2"/>
+      <c r="E61" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
@@ -7963,10 +7996,12 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>272</v>
+        <v>85</v>
       </c>
       <c r="L61" s="2"/>
-      <c r="M61" s="2"/>
+      <c r="M61" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -7977,7 +8012,7 @@
         <v>74</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>74</v>
+        <v>269</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>74</v>
@@ -7992,11 +8027,13 @@
         <v>74</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y61" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z61" t="s" s="2">
-        <v>273</v>
+        <v>74</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>74</v>
@@ -8014,7 +8051,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>271</v>
+        <v>179</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -8034,21 +8071,23 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E62" s="2"/>
+      <c r="E62" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>74</v>
@@ -8060,10 +8099,12 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>275</v>
+        <v>112</v>
       </c>
       <c r="L62" s="2"/>
-      <c r="M62" s="2"/>
+      <c r="M62" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8113,7 +8154,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>274</v>
+        <v>183</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -8133,21 +8174,23 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E63" s="2"/>
+      <c r="E63" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>74</v>
@@ -8159,10 +8202,12 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
+      <c r="M63" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8188,11 +8233,13 @@
         <v>74</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y63" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z63" t="s" s="2">
-        <v>277</v>
+        <v>74</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>74</v>
@@ -8210,7 +8257,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>276</v>
+        <v>187</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -8228,26 +8275,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E64" s="2"/>
+      <c r="E64" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="F64" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>74</v>
@@ -8256,13 +8305,11 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>280</v>
+        <v>190</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8313,13 +8360,13 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>278</v>
+        <v>191</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>74</v>
@@ -8333,23 +8380,23 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>74</v>
@@ -8361,11 +8408,11 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>86</v>
+        <v>194</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8392,11 +8439,13 @@
         <v>74</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -8414,7 +8463,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>89</v>
+        <v>195</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8434,18 +8483,16 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E66" t="s" s="2">
-        <v>62</v>
-      </c>
+      <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
@@ -8462,11 +8509,11 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>85</v>
+        <v>197</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8517,7 +8564,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8537,18 +8584,16 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E67" t="s" s="2">
-        <v>233</v>
-      </c>
+      <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
@@ -8565,11 +8610,11 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8620,7 +8665,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8640,23 +8685,23 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E68" t="s" s="2">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>74</v>
@@ -8668,11 +8713,11 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>102</v>
+        <v>205</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8723,7 +8768,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8743,23 +8788,23 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E69" t="s" s="2">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>74</v>
@@ -8771,11 +8816,11 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>102</v>
+        <v>210</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" t="s" s="2">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8826,13 +8871,13 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>74</v>
@@ -8846,23 +8891,23 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E70" t="s" s="2">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>74</v>
@@ -8874,11 +8919,11 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8929,13 +8974,13 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>74</v>
@@ -8947,12 +8992,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8960,13 +9005,13 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>74</v>
@@ -8975,11 +9020,13 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="L71" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="M71" t="s" s="2">
-        <v>250</v>
+        <v>281</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9030,7 +9077,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -9050,10 +9097,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9076,12 +9123,10 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>102</v>
+        <v>283</v>
       </c>
       <c r="L72" s="2"/>
-      <c r="M72" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="M72" s="2"/>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9107,13 +9152,11 @@
         <v>74</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>74</v>
+        <v>284</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>74</v>
@@ -9131,7 +9174,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>254</v>
+        <v>282</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -9149,20 +9192,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E73" t="s" s="2">
-        <v>256</v>
-      </c>
+      <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
@@ -9170,7 +9211,7 @@
         <v>75</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>74</v>
@@ -9179,12 +9220,10 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>179</v>
+        <v>286</v>
       </c>
       <c r="L73" s="2"/>
-      <c r="M73" t="s" s="2">
-        <v>257</v>
-      </c>
+      <c r="M73" s="2"/>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -9234,7 +9273,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -9254,18 +9293,16 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E74" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
@@ -9282,12 +9319,10 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="L74" s="2"/>
-      <c r="M74" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M74" s="2"/>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9317,7 +9352,7 @@
       </c>
       <c r="Y74" s="2"/>
       <c r="Z74" t="s" s="2">
-        <v>88</v>
+        <v>288</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>74</v>
@@ -9335,7 +9370,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>89</v>
+        <v>287</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9353,28 +9388,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E75" t="s" s="2">
-        <v>183</v>
-      </c>
+      <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>74</v>
@@ -9383,11 +9416,13 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L75" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="M75" t="s" s="2">
-        <v>184</v>
+        <v>291</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9414,11 +9449,13 @@
         <v>74</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y75" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z75" t="s" s="2">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>74</v>
@@ -9436,13 +9473,13 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>186</v>
+        <v>289</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>74</v>
@@ -9466,7 +9503,7 @@
         <v>74</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>80</v>
@@ -9484,11 +9521,11 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" t="s" s="2">
-        <v>190</v>
+        <v>86</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9515,13 +9552,11 @@
         <v>74</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>74</v>
@@ -9539,7 +9574,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>191</v>
+        <v>89</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9569,7 +9604,7 @@
         <v>74</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>193</v>
+        <v>62</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>80</v>
@@ -9591,7 +9626,7 @@
       </c>
       <c r="L77" s="2"/>
       <c r="M77" t="s" s="2">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9618,11 +9653,13 @@
         <v>74</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y77" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z77" t="s" s="2">
-        <v>195</v>
+        <v>74</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>74</v>
@@ -9640,7 +9677,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9670,7 +9707,7 @@
         <v>74</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>80</v>
@@ -9688,11 +9725,11 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9743,7 +9780,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9773,7 +9810,7 @@
         <v>74</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>80</v>
@@ -9791,11 +9828,11 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9822,11 +9859,13 @@
         <v>74</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>204</v>
+        <v>74</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -9844,7 +9883,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9873,7 +9912,9 @@
       <c r="D80" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E80" s="2"/>
+      <c r="E80" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
@@ -9890,10 +9931,12 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
+      <c r="M80" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -9919,11 +9962,13 @@
         <v>74</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>207</v>
+        <v>74</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>74</v>
@@ -9941,7 +9986,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9970,7 +10015,9 @@
       <c r="D81" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E81" s="2"/>
+      <c r="E81" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
@@ -9989,15 +10036,11 @@
       <c r="K81" t="s" s="2">
         <v>102</v>
       </c>
-      <c r="L81" t="s" s="2">
-        <v>210</v>
-      </c>
+      <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>74</v>
@@ -10046,7 +10089,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -10075,11 +10118,9 @@
       <c r="D82" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E82" t="s" s="2">
-        <v>215</v>
-      </c>
+      <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>75</v>
@@ -10094,11 +10135,11 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10149,7 +10190,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -10178,9 +10219,7 @@
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E83" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
@@ -10197,11 +10236,11 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10252,7 +10291,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10270,7 +10309,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>300</v>
       </c>
@@ -10282,16 +10321,16 @@
         <v>74</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>260</v>
+        <v>204</v>
       </c>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>74</v>
@@ -10300,11 +10339,11 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>261</v>
+        <v>205</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>262</v>
+        <v>206</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10355,13 +10394,13 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>263</v>
+        <v>207</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>74</v>
@@ -10385,13 +10424,13 @@
         <v>74</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>265</v>
+        <v>84</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>74</v>
@@ -10403,11 +10442,11 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" t="s" s="2">
-        <v>266</v>
+        <v>86</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10434,13 +10473,11 @@
         <v>74</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>74</v>
@@ -10458,13 +10495,13 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>267</v>
+        <v>89</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>74</v>
@@ -10476,7 +10513,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
         <v>302</v>
       </c>
@@ -10487,7 +10524,9 @@
       <c r="D86" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E86" s="2"/>
+      <c r="E86" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="F86" t="s" s="2">
         <v>80</v>
       </c>
@@ -10495,7 +10534,7 @@
         <v>75</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>74</v>
@@ -10504,13 +10543,11 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L86" s="2"/>
       <c r="M86" t="s" s="2">
-        <v>304</v>
+        <v>224</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10541,7 +10578,7 @@
       </c>
       <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>305</v>
+        <v>225</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>74</v>
@@ -10559,13 +10596,13 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>302</v>
+        <v>226</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>74</v>
@@ -10579,21 +10616,23 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E87" s="2"/>
+      <c r="E87" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>74</v>
@@ -10605,10 +10644,12 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>272</v>
+        <v>229</v>
       </c>
       <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
+      <c r="M87" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -10634,11 +10675,13 @@
         <v>74</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y87" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z87" t="s" s="2">
-        <v>307</v>
+        <v>74</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>74</v>
@@ -10656,13 +10699,13 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>306</v>
+        <v>231</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>74</v>
@@ -10676,21 +10719,23 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E88" s="2"/>
+      <c r="E88" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>74</v>
@@ -10702,11 +10747,11 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>309</v>
+        <v>234</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10733,13 +10778,11 @@
         <v>74</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y88" s="2"/>
       <c r="Z88" t="s" s="2">
-        <v>74</v>
+        <v>235</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>74</v>
@@ -10757,13 +10800,13 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>308</v>
+        <v>236</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>74</v>
@@ -10777,16 +10820,18 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E89" s="2"/>
+      <c r="E89" t="s" s="2">
+        <v>238</v>
+      </c>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
@@ -10803,10 +10848,12 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>311</v>
+        <v>85</v>
       </c>
       <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
+      <c r="M89" t="s" s="2">
+        <v>239</v>
+      </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -10856,7 +10903,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>310</v>
+        <v>240</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10876,21 +10923,23 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E90" s="2"/>
+      <c r="E90" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="F90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>74</v>
@@ -10902,10 +10951,12 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>313</v>
+        <v>85</v>
       </c>
       <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
+      <c r="M90" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -10931,13 +10982,11 @@
         <v>74</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y90" s="2"/>
       <c r="Z90" t="s" s="2">
-        <v>74</v>
+        <v>244</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>74</v>
@@ -10955,13 +11004,13 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>312</v>
+        <v>245</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>74</v>
@@ -10975,10 +11024,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10989,7 +11038,7 @@
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>74</v>
@@ -11001,7 +11050,7 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>315</v>
+        <v>85</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -11030,13 +11079,11 @@
         <v>74</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>74</v>
+        <v>247</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>74</v>
@@ -11054,13 +11101,13 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>314</v>
+        <v>248</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>74</v>
@@ -11074,10 +11121,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11088,7 +11135,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>74</v>
@@ -11100,11 +11147,17 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
-      <c r="N92" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>74</v>
@@ -11153,13 +11206,13 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>316</v>
+        <v>253</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>74</v>
@@ -11173,21 +11226,23 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E93" s="2"/>
+      <c r="E93" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="F93" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>74</v>
@@ -11199,10 +11254,12 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>319</v>
+        <v>256</v>
       </c>
       <c r="L93" s="2"/>
-      <c r="M93" s="2"/>
+      <c r="M93" t="s" s="2">
+        <v>257</v>
+      </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11252,13 +11309,13 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>318</v>
+        <v>258</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>74</v>
@@ -11272,21 +11329,23 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E94" s="2"/>
+      <c r="E94" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="F94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>74</v>
@@ -11298,10 +11357,12 @@
         <v>74</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>321</v>
+        <v>205</v>
       </c>
       <c r="L94" s="2"/>
-      <c r="M94" s="2"/>
+      <c r="M94" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -11351,13 +11412,13 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>320</v>
+        <v>262</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>74</v>
@@ -11371,16 +11432,18 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E95" s="2"/>
+      <c r="E95" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="F95" t="s" s="2">
         <v>80</v>
       </c>
@@ -11388,7 +11451,7 @@
         <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>74</v>
@@ -11397,10 +11460,12 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>323</v>
+        <v>210</v>
       </c>
       <c r="L95" s="2"/>
-      <c r="M95" s="2"/>
+      <c r="M95" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -11438,17 +11503,19 @@
         <v>74</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AC95" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD95" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>322</v>
+        <v>212</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11468,18 +11535,18 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E96" s="2"/>
+      <c r="E96" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
@@ -11496,12 +11563,12 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="M96" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="L96" s="2"/>
+      <c r="M96" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -11551,7 +11618,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>322</v>
+        <v>216</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11569,20 +11636,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E97" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>80</v>
       </c>
@@ -11590,7 +11655,7 @@
         <v>75</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>74</v>
@@ -11599,11 +11664,13 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L97" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>314</v>
+      </c>
       <c r="M97" t="s" s="2">
-        <v>86</v>
+        <v>315</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11634,7 +11701,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>88</v>
+        <v>316</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>74</v>
@@ -11652,13 +11719,13 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>89</v>
+        <v>313</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>74</v>
@@ -11672,10 +11739,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11698,12 +11765,10 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>91</v>
+        <v>283</v>
       </c>
       <c r="L98" s="2"/>
-      <c r="M98" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M98" s="2"/>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -11729,13 +11794,11 @@
         <v>74</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>74</v>
+        <v>318</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>74</v>
@@ -11753,7 +11816,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>93</v>
+        <v>317</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -11773,10 +11836,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>333</v>
+        <v>319</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11787,7 +11850,7 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>74</v>
@@ -11799,11 +11862,11 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" t="s" s="2">
-        <v>96</v>
+        <v>320</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11854,19 +11917,19 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>97</v>
+        <v>319</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>74</v>
@@ -11874,18 +11937,16 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E100" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
@@ -11902,12 +11963,10 @@
         <v>74</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>85</v>
+        <v>322</v>
       </c>
       <c r="L100" s="2"/>
-      <c r="M100" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M100" s="2"/>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -11933,11 +11992,13 @@
         <v>74</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y100" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z100" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>74</v>
@@ -11955,7 +12016,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>89</v>
+        <v>321</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11975,23 +12036,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E101" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>74</v>
@@ -12003,12 +12062,10 @@
         <v>74</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>102</v>
+        <v>324</v>
       </c>
       <c r="L101" s="2"/>
-      <c r="M101" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M101" s="2"/>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -12058,13 +12115,13 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>104</v>
+        <v>323</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>74</v>
@@ -12078,23 +12135,21 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>339</v>
+        <v>325</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E102" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>74</v>
@@ -12106,12 +12161,10 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>107</v>
+        <v>326</v>
       </c>
       <c r="L102" s="2"/>
-      <c r="M102" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M102" s="2"/>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -12161,13 +12214,13 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>109</v>
+        <v>325</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>74</v>
@@ -12181,23 +12234,21 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E103" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>74</v>
@@ -12209,12 +12260,10 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>112</v>
+        <v>328</v>
       </c>
       <c r="L103" s="2"/>
-      <c r="M103" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M103" s="2"/>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -12222,7 +12271,7 @@
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>74</v>
@@ -12264,13 +12313,13 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>115</v>
+        <v>327</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>74</v>
@@ -12284,23 +12333,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E104" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>74</v>
@@ -12312,12 +12359,10 @@
         <v>74</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>102</v>
+        <v>330</v>
       </c>
       <c r="L104" s="2"/>
-      <c r="M104" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M104" s="2"/>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -12367,13 +12412,13 @@
         <v>74</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>119</v>
+        <v>329</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>74</v>
@@ -12387,10 +12432,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12413,12 +12458,10 @@
         <v>74</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>95</v>
+        <v>332</v>
       </c>
       <c r="L105" s="2"/>
-      <c r="M105" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M105" s="2"/>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -12468,7 +12511,7 @@
         <v>74</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>125</v>
+        <v>331</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -12488,10 +12531,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12499,13 +12542,13 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>74</v>
@@ -12514,7 +12557,7 @@
         <v>74</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>85</v>
+        <v>334</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" s="2"/>
@@ -12528,7 +12571,7 @@
         <v>74</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>348</v>
+        <v>74</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>74</v>
@@ -12543,35 +12586,35 @@
         <v>74</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y106" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z106" t="s" s="2">
-        <v>349</v>
+        <v>74</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="AC106" s="2"/>
       <c r="AD106" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>74</v>
@@ -12585,12 +12628,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C107" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>337</v>
+      </c>
       <c r="D107" t="s" s="2">
         <v>74</v>
       </c>
@@ -12599,7 +12644,7 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>74</v>
@@ -12611,12 +12656,12 @@
         <v>74</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L107" s="2"/>
-      <c r="M107" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -12627,7 +12672,7 @@
         <v>74</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>74</v>
@@ -12666,13 +12711,13 @@
         <v>74</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>74</v>
@@ -12686,16 +12731,18 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E108" s="2"/>
+      <c r="E108" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F108" t="s" s="2">
         <v>80</v>
       </c>
@@ -12712,16 +12759,16 @@
         <v>74</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" t="s" s="2">
-        <v>357</v>
+        <v>86</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
-        <v>358</v>
+        <v>74</v>
       </c>
       <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
@@ -12743,13 +12790,11 @@
         <v>74</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>74</v>
@@ -12767,7 +12812,7 @@
         <v>74</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>359</v>
+        <v>89</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -12787,10 +12832,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12801,7 +12846,7 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>74</v>
@@ -12813,10 +12858,12 @@
         <v>74</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L109" s="2"/>
-      <c r="M109" s="2"/>
+      <c r="M109" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -12866,13 +12913,13 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>362</v>
+        <v>93</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>74</v>
@@ -12886,10 +12933,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12912,10 +12959,12 @@
         <v>74</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>365</v>
+        <v>95</v>
       </c>
       <c r="L110" s="2"/>
-      <c r="M110" s="2"/>
+      <c r="M110" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -12965,7 +13014,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>366</v>
+        <v>97</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -12977,7 +13026,7 @@
         <v>74</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>74</v>
@@ -12985,16 +13034,18 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E111" s="2"/>
+      <c r="E111" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F111" t="s" s="2">
         <v>80</v>
       </c>
@@ -13011,10 +13062,12 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>369</v>
+        <v>85</v>
       </c>
       <c r="L111" s="2"/>
-      <c r="M111" s="2"/>
+      <c r="M111" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -13040,13 +13093,11 @@
         <v>74</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>74</v>
@@ -13064,7 +13115,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>370</v>
+        <v>89</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -13084,16 +13135,18 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>371</v>
+        <v>347</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E112" s="2"/>
+      <c r="E112" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F112" t="s" s="2">
         <v>80</v>
       </c>
@@ -13110,10 +13163,12 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>373</v>
+        <v>102</v>
       </c>
       <c r="L112" s="2"/>
-      <c r="M112" s="2"/>
+      <c r="M112" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -13163,7 +13218,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>374</v>
+        <v>104</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13183,16 +13238,18 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>375</v>
+        <v>349</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>376</v>
+        <v>350</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E113" s="2"/>
+      <c r="E113" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F113" t="s" s="2">
         <v>80</v>
       </c>
@@ -13209,10 +13266,12 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>377</v>
+        <v>107</v>
       </c>
       <c r="L113" s="2"/>
-      <c r="M113" s="2"/>
+      <c r="M113" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -13262,7 +13321,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>378</v>
+        <v>109</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13282,18 +13341,20 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>379</v>
+        <v>351</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E114" s="2"/>
+      <c r="E114" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F114" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>75</v>
@@ -13308,10 +13369,12 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>381</v>
+        <v>112</v>
       </c>
       <c r="L114" s="2"/>
-      <c r="M114" s="2"/>
+      <c r="M114" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13319,7 +13382,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>74</v>
@@ -13361,7 +13424,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>382</v>
+        <v>115</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13381,18 +13444,20 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>383</v>
+        <v>353</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E115" s="2"/>
+      <c r="E115" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F115" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>75</v>
@@ -13407,10 +13472,12 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>385</v>
+        <v>102</v>
       </c>
       <c r="L115" s="2"/>
-      <c r="M115" s="2"/>
+      <c r="M115" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -13460,7 +13527,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>386</v>
+        <v>119</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -13480,10 +13547,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>387</v>
+        <v>355</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13494,7 +13561,7 @@
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>74</v>
@@ -13506,10 +13573,12 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>389</v>
+        <v>95</v>
       </c>
       <c r="L116" s="2"/>
-      <c r="M116" s="2"/>
+      <c r="M116" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -13559,13 +13628,13 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>390</v>
+        <v>125</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>74</v>
@@ -13579,10 +13648,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>392</v>
+        <v>358</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13590,7 +13659,7 @@
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G117" t="s" s="2">
         <v>75</v>
@@ -13605,7 +13674,7 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
@@ -13619,7 +13688,7 @@
         <v>74</v>
       </c>
       <c r="S117" t="s" s="2">
-        <v>74</v>
+        <v>359</v>
       </c>
       <c r="T117" t="s" s="2">
         <v>74</v>
@@ -13634,13 +13703,11 @@
         <v>74</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>74</v>
+        <v>360</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>74</v>
@@ -13658,10 +13725,10 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>394</v>
+        <v>361</v>
       </c>
       <c r="AG117" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH117" t="s" s="2">
         <v>75</v>
@@ -13678,10 +13745,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>395</v>
+        <v>362</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13704,10 +13771,12 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>397</v>
+        <v>107</v>
       </c>
       <c r="L118" s="2"/>
-      <c r="M118" s="2"/>
+      <c r="M118" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -13718,7 +13787,7 @@
         <v>74</v>
       </c>
       <c r="S118" t="s" s="2">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="T118" t="s" s="2">
         <v>74</v>
@@ -13757,7 +13826,7 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>398</v>
+        <v>365</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
@@ -13777,10 +13846,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>399</v>
+        <v>366</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>400</v>
+        <v>367</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13803,14 +13872,16 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>401</v>
+        <v>107</v>
       </c>
       <c r="L119" s="2"/>
-      <c r="M119" s="2"/>
+      <c r="M119" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
-        <v>74</v>
+        <v>369</v>
       </c>
       <c r="Q119" s="2"/>
       <c r="R119" t="s" s="2">
@@ -13856,7 +13927,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -13876,10 +13947,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13902,7 +13973,7 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -13955,7 +14026,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>406</v>
+        <v>373</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -13975,14 +14046,12 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>407</v>
+        <v>374</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>408</v>
-      </c>
+        <v>375</v>
+      </c>
+      <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>74</v>
       </c>
@@ -13991,7 +14060,7 @@
         <v>80</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>74</v>
@@ -14003,11 +14072,9 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>376</v>
+      </c>
+      <c r="L121" s="2"/>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -14058,13 +14125,13 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>322</v>
+        <v>377</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>74</v>
@@ -14078,18 +14145,16 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>410</v>
+        <v>378</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E122" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>80</v>
       </c>
@@ -14106,12 +14171,10 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>85</v>
+        <v>380</v>
       </c>
       <c r="L122" s="2"/>
-      <c r="M122" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M122" s="2"/>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14137,11 +14200,13 @@
         <v>74</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y122" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z122" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>74</v>
@@ -14159,7 +14224,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>89</v>
+        <v>381</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -14179,10 +14244,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>331</v>
+        <v>383</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14193,7 +14258,7 @@
         <v>80</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>74</v>
@@ -14205,12 +14270,10 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>91</v>
+        <v>384</v>
       </c>
       <c r="L123" s="2"/>
-      <c r="M123" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M123" s="2"/>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -14260,13 +14323,13 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>93</v>
+        <v>385</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>74</v>
@@ -14280,10 +14343,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>333</v>
+        <v>387</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14306,12 +14369,10 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>95</v>
+        <v>388</v>
       </c>
       <c r="L124" s="2"/>
-      <c r="M124" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M124" s="2"/>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -14361,7 +14422,7 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>97</v>
+        <v>389</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
@@ -14373,7 +14434,7 @@
         <v>74</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>74</v>
@@ -14381,18 +14442,16 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>413</v>
+        <v>390</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>335</v>
+        <v>391</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E125" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>80</v>
       </c>
@@ -14409,12 +14468,10 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>85</v>
+        <v>392</v>
       </c>
       <c r="L125" s="2"/>
-      <c r="M125" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M125" s="2"/>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -14440,11 +14497,13 @@
         <v>74</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y125" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z125" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>74</v>
@@ -14462,7 +14521,7 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>89</v>
+        <v>393</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -14482,18 +14541,16 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>337</v>
+        <v>395</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E126" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
         <v>80</v>
       </c>
@@ -14510,12 +14567,10 @@
         <v>74</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>102</v>
+        <v>396</v>
       </c>
       <c r="L126" s="2"/>
-      <c r="M126" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M126" s="2"/>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -14565,7 +14620,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>104</v>
+        <v>397</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14585,18 +14640,16 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>339</v>
+        <v>399</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E127" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>80</v>
       </c>
@@ -14613,12 +14666,10 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>107</v>
+        <v>400</v>
       </c>
       <c r="L127" s="2"/>
-      <c r="M127" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M127" s="2"/>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -14668,7 +14719,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>109</v>
+        <v>401</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14688,20 +14739,18 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>341</v>
+        <v>403</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E128" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>75</v>
@@ -14716,12 +14765,10 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>112</v>
+        <v>404</v>
       </c>
       <c r="L128" s="2"/>
-      <c r="M128" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M128" s="2"/>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -14729,7 +14776,7 @@
       </c>
       <c r="Q128" s="2"/>
       <c r="R128" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S128" t="s" s="2">
         <v>74</v>
@@ -14771,7 +14818,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>115</v>
+        <v>405</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -14791,20 +14838,18 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>343</v>
+        <v>407</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E129" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G129" t="s" s="2">
         <v>75</v>
@@ -14819,12 +14864,10 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>102</v>
+        <v>408</v>
       </c>
       <c r="L129" s="2"/>
-      <c r="M129" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M129" s="2"/>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -14874,7 +14917,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>119</v>
+        <v>409</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14894,10 +14937,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>345</v>
+        <v>411</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14908,7 +14951,7 @@
         <v>80</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>74</v>
@@ -14920,12 +14963,10 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>95</v>
+        <v>412</v>
       </c>
       <c r="L130" s="2"/>
-      <c r="M130" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M130" s="2"/>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -14975,13 +15016,13 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>125</v>
+        <v>413</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>74</v>
@@ -14995,10 +15036,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>347</v>
+        <v>415</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15006,7 +15047,7 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>75</v>
@@ -15021,7 +15062,7 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>85</v>
+        <v>416</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -15035,7 +15076,7 @@
         <v>74</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>420</v>
+        <v>74</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>74</v>
@@ -15050,11 +15091,13 @@
         <v>74</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y131" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z131" t="s" s="2">
-        <v>349</v>
+        <v>74</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>74</v>
@@ -15072,10 +15115,10 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>350</v>
+        <v>417</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>75</v>
@@ -15092,12 +15135,14 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="C132" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="D132" t="s" s="2">
         <v>74</v>
       </c>
@@ -15106,7 +15151,7 @@
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>74</v>
@@ -15118,12 +15163,12 @@
         <v>74</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L132" s="2"/>
-      <c r="M132" t="s" s="2">
-        <v>353</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M132" s="2"/>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -15134,7 +15179,7 @@
         <v>74</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>358</v>
+        <v>74</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>74</v>
@@ -15173,13 +15218,13 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>74</v>
@@ -15193,16 +15238,18 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E133" s="2"/>
+      <c r="E133" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F133" t="s" s="2">
         <v>80</v>
       </c>
@@ -15219,16 +15266,16 @@
         <v>74</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" t="s" s="2">
-        <v>357</v>
+        <v>86</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
-        <v>358</v>
+        <v>74</v>
       </c>
       <c r="Q133" s="2"/>
       <c r="R133" t="s" s="2">
@@ -15250,13 +15297,11 @@
         <v>74</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y133" s="2"/>
       <c r="Z133" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>74</v>
@@ -15274,7 +15319,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>359</v>
+        <v>89</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15294,10 +15339,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15308,7 +15353,7 @@
         <v>80</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>74</v>
@@ -15320,10 +15365,12 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="L134" s="2"/>
-      <c r="M134" s="2"/>
+      <c r="M134" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -15373,13 +15420,13 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>362</v>
+        <v>93</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>74</v>
@@ -15393,10 +15440,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15419,10 +15466,12 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>365</v>
+        <v>95</v>
       </c>
       <c r="L135" s="2"/>
-      <c r="M135" s="2"/>
+      <c r="M135" t="s" s="2">
+        <v>96</v>
+      </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -15472,7 +15521,7 @@
         <v>74</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>366</v>
+        <v>97</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>80</v>
@@ -15484,7 +15533,7 @@
         <v>74</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>74</v>
@@ -15492,16 +15541,18 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E136" s="2"/>
+      <c r="E136" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F136" t="s" s="2">
         <v>80</v>
       </c>
@@ -15518,10 +15569,12 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>369</v>
+        <v>85</v>
       </c>
       <c r="L136" s="2"/>
-      <c r="M136" s="2"/>
+      <c r="M136" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -15547,13 +15600,11 @@
         <v>74</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y136" s="2"/>
       <c r="Z136" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>74</v>
@@ -15571,7 +15622,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>370</v>
+        <v>89</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -15591,16 +15642,18 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>372</v>
+        <v>348</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E137" s="2"/>
+      <c r="E137" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F137" t="s" s="2">
         <v>80</v>
       </c>
@@ -15617,10 +15670,12 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>427</v>
+        <v>102</v>
       </c>
       <c r="L137" s="2"/>
-      <c r="M137" s="2"/>
+      <c r="M137" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -15670,7 +15725,7 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>374</v>
+        <v>104</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
@@ -15690,16 +15745,18 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>376</v>
+        <v>350</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E138" s="2"/>
+      <c r="E138" t="s" s="2">
+        <v>106</v>
+      </c>
       <c r="F138" t="s" s="2">
         <v>80</v>
       </c>
@@ -15716,10 +15773,12 @@
         <v>74</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>377</v>
+        <v>107</v>
       </c>
       <c r="L138" s="2"/>
-      <c r="M138" s="2"/>
+      <c r="M138" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -15769,7 +15828,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>378</v>
+        <v>109</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -15789,18 +15848,20 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E139" s="2"/>
+      <c r="E139" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="F139" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G139" t="s" s="2">
         <v>75</v>
@@ -15815,10 +15876,12 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>430</v>
+        <v>112</v>
       </c>
       <c r="L139" s="2"/>
-      <c r="M139" s="2"/>
+      <c r="M139" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -15826,7 +15889,7 @@
       </c>
       <c r="Q139" s="2"/>
       <c r="R139" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S139" t="s" s="2">
         <v>74</v>
@@ -15868,7 +15931,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>382</v>
+        <v>115</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -15888,18 +15951,20 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E140" s="2"/>
+      <c r="E140" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F140" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>75</v>
@@ -15914,10 +15979,12 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>385</v>
+        <v>102</v>
       </c>
       <c r="L140" s="2"/>
-      <c r="M140" s="2"/>
+      <c r="M140" t="s" s="2">
+        <v>118</v>
+      </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
       <c r="P140" t="s" s="2">
@@ -15967,7 +16034,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>386</v>
+        <v>119</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -15987,10 +16054,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16001,7 +16068,7 @@
         <v>80</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>74</v>
@@ -16013,10 +16080,12 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>389</v>
+        <v>95</v>
       </c>
       <c r="L141" s="2"/>
-      <c r="M141" s="2"/>
+      <c r="M141" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
@@ -16066,13 +16135,13 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>390</v>
+        <v>125</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>74</v>
@@ -16086,10 +16155,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>392</v>
+        <v>358</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16097,7 +16166,7 @@
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>75</v>
@@ -16112,7 +16181,7 @@
         <v>74</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>393</v>
+        <v>85</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" s="2"/>
@@ -16126,7 +16195,7 @@
         <v>74</v>
       </c>
       <c r="S142" t="s" s="2">
-        <v>74</v>
+        <v>431</v>
       </c>
       <c r="T142" t="s" s="2">
         <v>74</v>
@@ -16141,13 +16210,11 @@
         <v>74</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>74</v>
+        <v>360</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>74</v>
@@ -16165,10 +16232,10 @@
         <v>74</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>394</v>
+        <v>361</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>75</v>
@@ -16185,10 +16252,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>396</v>
+        <v>363</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16211,10 +16278,12 @@
         <v>74</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>397</v>
+        <v>107</v>
       </c>
       <c r="L143" s="2"/>
-      <c r="M143" s="2"/>
+      <c r="M143" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -16225,7 +16294,7 @@
         <v>74</v>
       </c>
       <c r="S143" t="s" s="2">
-        <v>74</v>
+        <v>369</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>74</v>
@@ -16264,7 +16333,7 @@
         <v>74</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>398</v>
+        <v>365</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
@@ -16284,10 +16353,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>400</v>
+        <v>367</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16310,14 +16379,16 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>401</v>
+        <v>107</v>
       </c>
       <c r="L144" s="2"/>
-      <c r="M144" s="2"/>
+      <c r="M144" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
-        <v>74</v>
+        <v>369</v>
       </c>
       <c r="Q144" s="2"/>
       <c r="R144" t="s" s="2">
@@ -16363,7 +16434,7 @@
         <v>74</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -16383,10 +16454,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16409,7 +16480,7 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>405</v>
+        <v>107</v>
       </c>
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
@@ -16462,7 +16533,7 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>406</v>
+        <v>373</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
@@ -16482,10 +16553,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>437</v>
+        <v>375</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16496,7 +16567,7 @@
         <v>80</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>74</v>
@@ -16508,7 +16579,7 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>438</v>
+        <v>376</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16561,13 +16632,13 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>437</v>
+        <v>377</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>74</v>
@@ -16581,10 +16652,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>439</v>
+        <v>379</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16595,7 +16666,7 @@
         <v>80</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>74</v>
@@ -16607,7 +16678,7 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>440</v>
+        <v>380</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" s="2"/>
@@ -16660,13 +16731,13 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>439</v>
+        <v>381</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>74</v>
@@ -16680,10 +16751,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>441</v>
+        <v>383</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -16694,7 +16765,7 @@
         <v>80</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>74</v>
@@ -16706,7 +16777,7 @@
         <v>74</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" s="2"/>
@@ -16759,13 +16830,13 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>441</v>
+        <v>385</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH148" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI148" t="s" s="2">
         <v>74</v>
@@ -16779,10 +16850,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>443</v>
+        <v>387</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -16793,7 +16864,7 @@
         <v>80</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>74</v>
@@ -16805,12 +16876,10 @@
         <v>74</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>444</v>
+        <v>388</v>
       </c>
       <c r="L149" s="2"/>
-      <c r="M149" t="s" s="2">
-        <v>445</v>
-      </c>
+      <c r="M149" s="2"/>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
@@ -16860,13 +16929,13 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>443</v>
+        <v>389</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>74</v>
@@ -16880,18 +16949,16 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>446</v>
+        <v>391</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E150" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>80</v>
       </c>
@@ -16908,12 +16975,10 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>85</v>
+        <v>441</v>
       </c>
       <c r="L150" s="2"/>
-      <c r="M150" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M150" s="2"/>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -16939,11 +17004,13 @@
         <v>74</v>
       </c>
       <c r="X150" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y150" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z150" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>74</v>
@@ -16961,7 +17028,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>89</v>
+        <v>393</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -16981,10 +17048,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>447</v>
+        <v>395</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -16995,7 +17062,7 @@
         <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>74</v>
@@ -17007,12 +17074,10 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>91</v>
+        <v>396</v>
       </c>
       <c r="L151" s="2"/>
-      <c r="M151" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M151" s="2"/>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -17062,13 +17127,13 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>93</v>
+        <v>397</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI151" t="s" s="2">
         <v>74</v>
@@ -17082,10 +17147,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>448</v>
+        <v>399</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17108,12 +17173,10 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>95</v>
+        <v>400</v>
       </c>
       <c r="L152" s="2"/>
-      <c r="M152" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M152" s="2"/>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -17163,7 +17226,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>97</v>
+        <v>401</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17175,7 +17238,7 @@
         <v>74</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>74</v>
@@ -17183,18 +17246,16 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>449</v>
+        <v>403</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E153" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E153" s="2"/>
       <c r="F153" t="s" s="2">
         <v>80</v>
       </c>
@@ -17211,12 +17272,10 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>85</v>
+        <v>404</v>
       </c>
       <c r="L153" s="2"/>
-      <c r="M153" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M153" s="2"/>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -17242,11 +17301,13 @@
         <v>74</v>
       </c>
       <c r="X153" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y153" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z153" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA153" t="s" s="2">
         <v>74</v>
@@ -17264,7 +17325,7 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>89</v>
+        <v>405</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
@@ -17284,18 +17345,16 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>450</v>
+        <v>407</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E154" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
         <v>80</v>
       </c>
@@ -17312,12 +17371,10 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>102</v>
+        <v>408</v>
       </c>
       <c r="L154" s="2"/>
-      <c r="M154" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M154" s="2"/>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -17367,7 +17424,7 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>104</v>
+        <v>409</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>80</v>
@@ -17387,18 +17444,16 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>451</v>
+        <v>411</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E155" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
         <v>80</v>
       </c>
@@ -17415,12 +17470,10 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>107</v>
+        <v>412</v>
       </c>
       <c r="L155" s="2"/>
-      <c r="M155" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M155" s="2"/>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -17470,7 +17523,7 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>109</v>
+        <v>413</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>80</v>
@@ -17490,20 +17543,18 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>452</v>
+        <v>415</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E156" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G156" t="s" s="2">
         <v>75</v>
@@ -17518,12 +17569,10 @@
         <v>74</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>112</v>
+        <v>416</v>
       </c>
       <c r="L156" s="2"/>
-      <c r="M156" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M156" s="2"/>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -17531,7 +17580,7 @@
       </c>
       <c r="Q156" s="2"/>
       <c r="R156" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S156" t="s" s="2">
         <v>74</v>
@@ -17573,7 +17622,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>115</v>
+        <v>417</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -17593,23 +17642,21 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E157" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>74</v>
@@ -17621,12 +17668,10 @@
         <v>74</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>102</v>
+        <v>449</v>
       </c>
       <c r="L157" s="2"/>
-      <c r="M157" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M157" s="2"/>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -17676,13 +17721,13 @@
         <v>74</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>119</v>
+        <v>448</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>74</v>
@@ -17696,10 +17741,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17722,12 +17767,10 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>95</v>
+        <v>451</v>
       </c>
       <c r="L158" s="2"/>
-      <c r="M158" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M158" s="2"/>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -17777,7 +17820,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>125</v>
+        <v>450</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -17797,10 +17840,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -17811,7 +17854,7 @@
         <v>80</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>74</v>
@@ -17823,7 +17866,7 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>85</v>
+        <v>453</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -17834,7 +17877,7 @@
       </c>
       <c r="Q159" s="2"/>
       <c r="R159" t="s" s="2">
-        <v>456</v>
+        <v>74</v>
       </c>
       <c r="S159" t="s" s="2">
         <v>74</v>
@@ -17852,11 +17895,13 @@
         <v>74</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y159" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z159" t="s" s="2">
-        <v>457</v>
+        <v>74</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>74</v>
@@ -17874,13 +17919,13 @@
         <v>74</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH159" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI159" t="s" s="2">
         <v>74</v>
@@ -17894,10 +17939,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -17905,10 +17950,10 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>74</v>
@@ -17920,10 +17965,12 @@
         <v>74</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="L160" s="2"/>
-      <c r="M160" s="2"/>
+      <c r="M160" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -17973,13 +18020,13 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH160" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI160" t="s" s="2">
         <v>74</v>
@@ -17993,21 +18040,23 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E161" s="2"/>
+      <c r="E161" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F161" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>74</v>
@@ -18019,10 +18068,12 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>461</v>
+        <v>85</v>
       </c>
       <c r="L161" s="2"/>
-      <c r="M161" s="2"/>
+      <c r="M161" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -18048,13 +18099,11 @@
         <v>74</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y161" s="2"/>
       <c r="Z161" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>74</v>
@@ -18072,26 +18121,1137 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG161" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH161" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI161" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ161" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK161" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="162" hidden="true">
+      <c r="A162" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B162" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C162" s="2"/>
+      <c r="D162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E162" s="2"/>
+      <c r="F162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K162" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L162" s="2"/>
+      <c r="M162" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N162" s="2"/>
+      <c r="O162" s="2"/>
+      <c r="P162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q162" s="2"/>
+      <c r="R162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF162" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG162" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH162" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ162" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK162" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="163" hidden="true">
+      <c r="A163" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="B163" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="C163" s="2"/>
+      <c r="D163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E163" s="2"/>
+      <c r="F163" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G163" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K163" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L163" s="2"/>
+      <c r="M163" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N163" s="2"/>
+      <c r="O163" s="2"/>
+      <c r="P163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q163" s="2"/>
+      <c r="R163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF163" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG163" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH163" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI163" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ163" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK163" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="164" hidden="true">
+      <c r="A164" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="AG161" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH161" t="s" s="2">
+      <c r="B164" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="C164" s="2"/>
+      <c r="D164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E164" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F164" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G164" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K164" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L164" s="2"/>
+      <c r="M164" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N164" s="2"/>
+      <c r="O164" s="2"/>
+      <c r="P164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q164" s="2"/>
+      <c r="R164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X164" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y164" s="2"/>
+      <c r="Z164" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF164" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG164" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH164" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ164" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK164" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="165" hidden="true">
+      <c r="A165" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B165" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C165" s="2"/>
+      <c r="D165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E165" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F165" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G165" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K165" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L165" s="2"/>
+      <c r="M165" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N165" s="2"/>
+      <c r="O165" s="2"/>
+      <c r="P165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q165" s="2"/>
+      <c r="R165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF165" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG165" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH165" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ165" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK165" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="166" hidden="true">
+      <c r="A166" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B166" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="C166" s="2"/>
+      <c r="D166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E166" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F166" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G166" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K166" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L166" s="2"/>
+      <c r="M166" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N166" s="2"/>
+      <c r="O166" s="2"/>
+      <c r="P166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q166" s="2"/>
+      <c r="R166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF166" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG166" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH166" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ166" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK166" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="167" hidden="true">
+      <c r="A167" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="B167" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="C167" s="2"/>
+      <c r="D167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E167" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F167" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G167" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K167" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L167" s="2"/>
+      <c r="M167" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N167" s="2"/>
+      <c r="O167" s="2"/>
+      <c r="P167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q167" s="2"/>
+      <c r="R167" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF167" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG167" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH167" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ167" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK167" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="168" hidden="true">
+      <c r="A168" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="B168" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C168" s="2"/>
+      <c r="D168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E168" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F168" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G168" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K168" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L168" s="2"/>
+      <c r="M168" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N168" s="2"/>
+      <c r="O168" s="2"/>
+      <c r="P168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q168" s="2"/>
+      <c r="R168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF168" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG168" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH168" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ168" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK168" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="169" hidden="true">
+      <c r="A169" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B169" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C169" s="2"/>
+      <c r="D169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E169" s="2"/>
+      <c r="F169" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G169" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI161" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ161" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK161" t="s" s="2">
+      <c r="H169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K169" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L169" s="2"/>
+      <c r="M169" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N169" s="2"/>
+      <c r="O169" s="2"/>
+      <c r="P169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q169" s="2"/>
+      <c r="R169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF169" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG169" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH169" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ169" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK169" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="170" hidden="true">
+      <c r="A170" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B170" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C170" s="2"/>
+      <c r="D170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E170" s="2"/>
+      <c r="F170" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G170" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K170" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L170" s="2"/>
+      <c r="M170" s="2"/>
+      <c r="N170" s="2"/>
+      <c r="O170" s="2"/>
+      <c r="P170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q170" s="2"/>
+      <c r="R170" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="S170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X170" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y170" s="2"/>
+      <c r="Z170" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AA170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF170" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="AG170" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH170" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ170" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK170" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="171" hidden="true">
+      <c r="A171" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B171" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C171" s="2"/>
+      <c r="D171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E171" s="2"/>
+      <c r="F171" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G171" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K171" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="L171" s="2"/>
+      <c r="M171" s="2"/>
+      <c r="N171" s="2"/>
+      <c r="O171" s="2"/>
+      <c r="P171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q171" s="2"/>
+      <c r="R171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF171" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AG171" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH171" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ171" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK171" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="172" hidden="true">
+      <c r="A172" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B172" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="C172" s="2"/>
+      <c r="D172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E172" s="2"/>
+      <c r="F172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K172" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="L172" s="2"/>
+      <c r="M172" s="2"/>
+      <c r="N172" s="2"/>
+      <c r="O172" s="2"/>
+      <c r="P172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q172" s="2"/>
+      <c r="R172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF172" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG172" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH172" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ172" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK172" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK161">
+  <autoFilter ref="A1:AK172">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18101,7 +19261,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI160">
+  <conditionalFormatting sqref="A2:AI171">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
